--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11037_MethodTables_UnreachableStatementValidation.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11037_MethodTables_UnreachableStatementValidation.xlsx
@@ -66,7 +66,7 @@
     <t>return;</t>
   </si>
   <si>
-    <t>for (int i = 0;true;i++)
+    <t>for (int i = 0;true;i += 1)
 {}</t>
   </si>
   <si>
